--- a/artfynd/A 56303-2025 artfynd.xlsx
+++ b/artfynd/A 56303-2025 artfynd.xlsx
@@ -3428,7 +3428,7 @@
         <v>133645549</v>
       </c>
       <c r="B25" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>133645450</v>
       </c>
       <c r="B26" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 56303-2025 artfynd.xlsx
+++ b/artfynd/A 56303-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131643351</v>
+        <v>131644383</v>
       </c>
       <c r="B2" t="n">
-        <v>93195</v>
+        <v>96413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4368</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470282</v>
+        <v>470254</v>
       </c>
       <c r="R2" t="n">
-        <v>6599300</v>
+        <v>6599260</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,64 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131641252</v>
+        <v>131642393</v>
       </c>
       <c r="B3" t="n">
-        <v>57136</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470182</v>
+        <v>470291</v>
       </c>
       <c r="R3" t="n">
-        <v>6599297</v>
+        <v>6599422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färsk spillning under betad tall.</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,64 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131644942</v>
+        <v>133645450</v>
       </c>
       <c r="B4" t="n">
-        <v>57136</v>
+        <v>93271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Vägtorpet, Norra Vägtorpet, Vrm</t>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470202</v>
+        <v>470125</v>
       </c>
       <c r="R4" t="n">
-        <v>6599226</v>
+        <v>6599402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,57 +974,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131640681</v>
+        <v>131643351</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>93289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pulshöjd, Pulshöjd, Vrm</t>
+          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470081</v>
+        <v>470282</v>
       </c>
       <c r="R5" t="n">
-        <v>6599307</v>
+        <v>6599300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,61 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131643650</v>
+        <v>131640681</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470293</v>
+        <v>470081</v>
       </c>
       <c r="R6" t="n">
-        <v>6599283</v>
+        <v>6599307</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår av födosök efter barkborrar i torrgran.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131641170</v>
+        <v>131642800</v>
       </c>
       <c r="B7" t="n">
-        <v>57136</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,53 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470192</v>
+        <v>470296</v>
       </c>
       <c r="R7" t="n">
-        <v>6599269</v>
+        <v>6599294</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1373,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131642800</v>
+        <v>131643739</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470296</v>
+        <v>470305</v>
       </c>
       <c r="R8" t="n">
-        <v>6599294</v>
+        <v>6599257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1417,7 @@
         <v>131644678</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131640730</v>
+        <v>133645549</v>
       </c>
       <c r="B10" t="n">
-        <v>57136</v>
+        <v>91937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,53 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470109</v>
+        <v>470112</v>
       </c>
       <c r="R10" t="n">
-        <v>6599307</v>
+        <v>6599284</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,22 +1606,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jim Hellquist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131641018</v>
+        <v>131642448</v>
       </c>
       <c r="B11" t="n">
-        <v>57136</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1778,27 +1656,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470170</v>
+        <v>470303</v>
       </c>
       <c r="R11" t="n">
-        <v>6599294</v>
+        <v>6599374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,7 +1702,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,12 +1712,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning under kraftigt tjäderbetad tall.</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,41 +1739,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131642903</v>
+        <v>131643822</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470305</v>
+        <v>470297</v>
       </c>
       <c r="R12" t="n">
-        <v>6599280</v>
+        <v>6599249</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1833,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår av födosök efter hästmyror.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131641642</v>
+        <v>131644433</v>
       </c>
       <c r="B13" t="n">
-        <v>57136</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2013,14 +1903,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2029,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470204</v>
+        <v>470259</v>
       </c>
       <c r="R13" t="n">
-        <v>6599383</v>
+        <v>6599267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2064,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2074,7 +1959,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Överflygande.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,45 +1991,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131644383</v>
+        <v>131643650</v>
       </c>
       <c r="B14" t="n">
-        <v>96315</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470254</v>
+        <v>470293</v>
       </c>
       <c r="R14" t="n">
-        <v>6599260</v>
+        <v>6599283</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2087,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spår av födosök efter barkborrar i torrgran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131641723</v>
+        <v>131640548</v>
       </c>
       <c r="B15" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,19 +2164,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470209</v>
+        <v>470036</v>
       </c>
       <c r="R15" t="n">
-        <v>6599459</v>
+        <v>6599308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2208,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,7 +2218,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Under betad äldre tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2334,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131642393</v>
+        <v>131640730</v>
       </c>
       <c r="B16" t="n">
-        <v>93177</v>
+        <v>57162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,34 +2261,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470291</v>
+        <v>470109</v>
       </c>
       <c r="R16" t="n">
-        <v>6599422</v>
+        <v>6599307</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,7 +2339,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,7 +2349,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,32 +2376,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131642448</v>
+        <v>131641018</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2479,21 +2414,27 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470303</v>
+        <v>470170</v>
       </c>
       <c r="R17" t="n">
-        <v>6599374</v>
+        <v>6599294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2476,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning under kraftigt tjäderbetad tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,32 +2508,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131644433</v>
+        <v>131641079</v>
       </c>
       <c r="B18" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2600,9 +2546,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2611,10 +2562,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470259</v>
+        <v>470171</v>
       </c>
       <c r="R18" t="n">
-        <v>6599267</v>
+        <v>6599293</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2646,7 +2597,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,12 +2607,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Överflygande.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131641602</v>
+        <v>131641152</v>
       </c>
       <c r="B19" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2742,10 +2688,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470199</v>
+        <v>470195</v>
       </c>
       <c r="R19" t="n">
-        <v>6599383</v>
+        <v>6599275</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,7 +2723,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2787,7 +2733,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,10 +2760,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131641079</v>
+        <v>131641170</v>
       </c>
       <c r="B20" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2868,10 +2814,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470171</v>
+        <v>470192</v>
       </c>
       <c r="R20" t="n">
-        <v>6599293</v>
+        <v>6599269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2903,7 +2849,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2913,7 +2859,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131643739</v>
+        <v>131641252</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,34 +2897,53 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470305</v>
+        <v>470182</v>
       </c>
       <c r="R21" t="n">
-        <v>6599257</v>
+        <v>6599297</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3010,7 +2975,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3020,7 +2985,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färsk spillning under betad tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,10 +3017,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131641152</v>
+        <v>131641565</v>
       </c>
       <c r="B22" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3092,7 +3062,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3101,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470195</v>
+        <v>470178</v>
       </c>
       <c r="R22" t="n">
-        <v>6599275</v>
+        <v>6599377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3136,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3146,7 +3116,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,32 +3143,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131643822</v>
+        <v>131641602</v>
       </c>
       <c r="B23" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3211,9 +3181,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3222,10 +3197,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>470297</v>
+        <v>470199</v>
       </c>
       <c r="R23" t="n">
-        <v>6599249</v>
+        <v>6599383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3257,7 +3232,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3267,12 +3242,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spår av födosök efter hästmyror.</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3299,10 +3269,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131641565</v>
+        <v>131641642</v>
       </c>
       <c r="B24" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3344,7 +3314,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3353,10 +3323,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470178</v>
+        <v>470204</v>
       </c>
       <c r="R24" t="n">
-        <v>6599377</v>
+        <v>6599383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3388,7 +3358,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3398,7 +3368,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3425,10 +3395,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133645549</v>
+        <v>131641723</v>
       </c>
       <c r="B25" t="n">
-        <v>91930</v>
+        <v>57162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,34 +3406,53 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470112</v>
+        <v>470209</v>
       </c>
       <c r="R25" t="n">
-        <v>6599284</v>
+        <v>6599459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,12 +3479,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3510,22 +3509,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133645450</v>
+        <v>131642023</v>
       </c>
       <c r="B26" t="n">
-        <v>93264</v>
+        <v>57162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3533,34 +3532,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pulshöjd, Pulshöjd, Vrm</t>
+          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470125</v>
+        <v>470231</v>
       </c>
       <c r="R26" t="n">
-        <v>6599402</v>
+        <v>6599523</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3587,12 +3605,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spillning under tjäderbetad tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3607,15 +3640,514 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131642132</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>470240</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6599553</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131642163</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mördingsmossen, Mördingsmossen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>470238</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6599557</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131644942</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norra Vägtorpet, Norra Vägtorpet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>470202</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6599226</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131639523</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57165</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pulshöjd, Pulshöjd, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>470081</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6599724</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Storfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kroppa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56303-2025 artfynd.xlsx
+++ b/artfynd/A 56303-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131644383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642393</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131643351</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131640681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131643739</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131644678</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645549</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642448</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131643822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131644433</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131643650</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131640548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2373,6 +2448,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131640730</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2505,6 +2585,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641018</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2631,6 +2716,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641079</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2757,6 +2847,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641152</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2883,6 +2978,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641170</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3014,6 +3114,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641252</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3140,6 +3245,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641565</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3266,6 +3376,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641602</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3392,6 +3507,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641642</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3518,6 +3638,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131641723</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3649,6 +3774,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642023</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3775,6 +3905,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642132</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3901,6 +4036,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131642163</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4027,6 +4167,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131644942</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4148,8 +4293,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131639523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>